--- a/mapping/Vertebrate_Mammalian.xlsx
+++ b/mapping/Vertebrate_Mammalian.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B169"/>
+  <dimension ref="A1:B173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>小囊鼠属</t>
+          <t>囊鼠属</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>中喙鲸属</t>
+          <t>喙鲸属</t>
         </is>
       </c>
     </row>
@@ -2387,58 +2387,106 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Lontra</t>
+          <t>Galeopterus</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>水獭属</t>
+          <t>鼯猴属</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Leopardus</t>
+          <t>Lontra</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>虎猫属</t>
+          <t>水獭属</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Fukomys</t>
+          <t>Pteronotus</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>隐鼠属</t>
+          <t>兔唇蝠属</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Pipistrellus</t>
+          <t>Leopardus</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>伏翼属</t>
+          <t>虎猫属</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>Pipistrellus</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>伏翼属</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Miniopterus</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>长翼蝠属</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Phascolarctos</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>树袋熊属</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Fukomys</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>隐鼠属</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>Molossus</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>皱唇蝠属</t>
         </is>
